--- a/AAII_Financials/Quarterly/NSTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NSTB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>NSTB</t>
   </si>
@@ -1178,8 +1178,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>100</v>
       </c>
       <c r="E17" s="3">
         <v>100</v>
@@ -1480,8 +1480,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-100</v>
       </c>
       <c r="E23" s="3">
         <v>300</v>
@@ -1648,8 +1648,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-100</v>
       </c>
       <c r="E26" s="3">
         <v>300</v>
@@ -1704,8 +1704,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-100</v>
       </c>
       <c r="E27" s="3">
         <v>300</v>
@@ -2040,8 +2040,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-100</v>
       </c>
       <c r="E33" s="3">
         <v>300</v>
@@ -2152,8 +2152,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-100</v>
       </c>
       <c r="E35" s="3">
         <v>300</v>
@@ -3254,7 +3254,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
@@ -4171,8 +4171,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>-400</v>
       </c>
       <c r="E76" s="3">
         <v>4400</v>
@@ -4344,8 +4344,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-100</v>
       </c>
       <c r="E81" s="3">
         <v>300</v>
@@ -5418,8 +5418,8 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
         <v>200</v>
